--- a/TP4/tabla_diff_medias_train_vs_test_2005.xlsx
+++ b/TP4/tabla_diff_medias_train_vs_test_2005.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,23 +473,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>edad</t>
+          <t>edad2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.54634931997137</v>
+        <v>1658.640121689334</v>
       </c>
       <c r="C2" t="n">
-        <v>34.99666110183639</v>
+        <v>1703.818030050084</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4503117818650253</v>
+        <v>-45.17790836074914</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8460614238908871</v>
+        <v>-1.026394758680243</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3975637497079761</v>
+        <v>0.3047612411521702</v>
       </c>
       <c r="G2" t="n">
         <v>5588</v>
@@ -501,28 +501,552 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>estado_empleo</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.156109815180334</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.181475272422464</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.02536545724213068</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.9214907315071735</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3568431001276817</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5573</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>parentesco</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.046090387374462</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.084795321637427</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03870493426296528</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.8980945671865458</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.369183363030548</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5576</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>edad</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>34.54634931997137</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34.99666110183639</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.4503117818650253</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.8460614238908871</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3975637497079761</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nivel_ocupacion</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.232999284180386</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.307595993322204</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07459670914181782</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.8078277322150538</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4192394285454771</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>n_personas</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.322118826055834</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.292153589315526</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.02996523674030804</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7095383827657836</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4780272081933725</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tipo_cobertura_salud</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.651037938439513</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.642320534223706</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.008717404215807134</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6693676085326321</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5032956627829318</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>categoria_inactividad</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.61882605583393</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.646911519198665</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.02808546336473472</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.5962306991804702</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5510506838533576</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Distincion_vivienda_hogar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.046349319971367</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.049666110183639</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.003316790212272158</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.5774651906026715</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5636547962692862</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>medio_busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.03614889047959914</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04131886477462438</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.005169974295025234</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.5443866890340993</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5862029452169306</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>ad_equiv_hogar</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B12" t="n">
         <v>3.498101288475304</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C12" t="n">
         <v>3.479023372287146</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D12" t="n">
         <v>0.01907791618815846</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E12" t="n">
         <v>0.5409195394462607</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F12" t="n">
         <v>0.5885898015480266</v>
       </c>
-      <c r="G3" t="n">
-        <v>5588</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="G12" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>obra_social</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4906943450250537</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4845575959933222</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.006136749031731503</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3215620696827071</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7477981667985459</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nivel_educ</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.865783822476736</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.856427378964942</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.009356443511794321</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2102005316052259</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8335206013379997</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tipo_contrato</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.668217609162491</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.664858096828047</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.003359512334444315</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1125126098037934</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9104220168004165</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>horastrab</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>23.16839656406585</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23.04006677796327</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1283297861025829</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.05578570593764551</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9555150730509925</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.519863994273443</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.520450751252087</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.0005867569786437432</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.04808746618071206</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9616486542377281</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adulto_equiv</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.8159753042233358</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8158430717863105</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0001322324370252037</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.03517092967997969</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9719450098183646</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tipo_empleo</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.465103793843952</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.465776293823038</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.0006724999790868047</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.01731905942090302</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9861828473394605</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>educ</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9.988010021474588</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9.988731218697829</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.0007211972232408215</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.005540662462259992</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9955794571069876</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>empleo</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>5588</v>
+      </c>
+      <c r="H22" t="n">
         <v>2396</v>
       </c>
     </row>
